--- a/data/trans_orig/P56$nadie-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P56$nadie-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24586</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15378</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37092</t>
+          <t>37805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27599</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>44490</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57158</t>
+          <t>57687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24110</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>34420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>57,82%</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,97%</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21243</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14530</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>27529</t>
+          <t>26214</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17941</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>41080</t>
+          <t>42002</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>48161</t>
+          <t>48416</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>37203</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>59486</t>
+          <t>58298</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26329</t>
+          <t>25607</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>37377</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -4700,12 +4700,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4715,12 +4715,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -4848,12 +4848,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5520,77 +5520,77 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13452</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7357</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22878</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>15508</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>9241</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>9,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13452</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21120</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>15508</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>9019</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>24276</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>18887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37534</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38223</t>
+          <t>39340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40782</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69798</t>
+          <t>71774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39519</t>
+          <t>39571</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51861</t>
+          <t>52400</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81652</t>
+          <t>81356</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42291</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68762</t>
+          <t>67598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>58302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86561</t>
+          <t>86829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12672</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34911</t>
+          <t>34160</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42279</t>
+          <t>42903</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -6178,12 +6178,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>30344</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53179</t>
+          <t>53750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36405</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62887</t>
+          <t>64798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22064</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -9015,12 +9015,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>43177</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>40983</t>
+          <t>42143</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>49969</t>
+          <t>49615</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>78775</t>
+          <t>80663</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -9128,12 +9128,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>45416</t>
+          <t>45243</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>70799</t>
+          <t>71317</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>58692</t>
+          <t>58838</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>90201</t>
+          <t>90932</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -9241,12 +9241,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29885</t>
+          <t>29980</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>47028</t>
+          <t>45949</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>73133</t>
+          <t>71941</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>65057</t>
+          <t>65267</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>95954</t>
+          <t>95582</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -9467,12 +9467,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9502,12 +9502,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>39764</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>26278</t>
+          <t>25981</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>50572</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -9580,12 +9580,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9615,12 +9615,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>30536</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>55077</t>
+          <t>53720</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>36361</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>63752</t>
+          <t>62900</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10004,12 +10004,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32619</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -10380,12 +10380,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20101</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34317</t>
+          <t>34476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10415,12 +10415,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26477</t>
+          <t>26558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10430,12 +10430,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56208</t>
+          <t>56067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10465,12 +10465,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -10493,12 +10493,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10528,12 +10528,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27416</t>
+          <t>26177</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50738</t>
+          <t>51821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>37302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63434</t>
+          <t>62655</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -10606,12 +10606,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31717</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55250</t>
+          <t>54882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42724</t>
+          <t>41840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69279</t>
+          <t>70378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -10832,12 +10832,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>30897</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>38388</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -10945,12 +10945,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>22826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11436,12 +11436,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11451,12 +11451,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13226</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11486,12 +11486,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -11514,12 +11514,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11529,12 +11529,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11549,12 +11549,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11564,12 +11564,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11584,12 +11584,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11599,12 +11599,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11712,12 +11712,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -11780,7 +11780,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -11966,12 +11966,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11981,12 +11981,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12016,12 +12016,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -13669,12 +13669,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13684,12 +13684,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13704,12 +13704,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>41034</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13719,12 +13719,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13739,12 +13739,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>23786</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>47572</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13754,12 +13754,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -13782,12 +13782,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>25572</t>
+          <t>26789</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>43080</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35472</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>44807</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>72443</t>
+          <t>73099</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13867,12 +13867,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -13895,12 +13895,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>33698</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>59659</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>44872</t>
+          <t>45284</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>73135</t>
+          <t>73120</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -14008,12 +14008,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>56105</t>
+          <t>55836</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14078,12 +14078,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>42987</t>
+          <t>42208</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>70377</t>
+          <t>71623</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14093,12 +14093,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -14156,12 +14156,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14171,12 +14171,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14191,12 +14191,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -14234,12 +14234,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14269,12 +14269,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>39014</t>
+          <t>40246</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14284,12 +14284,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14304,12 +14304,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>25617</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>50892</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14319,12 +14319,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -14347,12 +14347,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -14382,12 +14382,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14397,12 +14397,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14417,12 +14417,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14432,12 +14432,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -14465,7 +14465,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -14691,7 +14691,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -14756,12 +14756,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -15029,32 +15029,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -15064,32 +15064,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -15099,32 +15099,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -15142,32 +15142,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>23490</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27899</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -15177,32 +15177,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28113</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22116</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15212,32 +15212,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>53844</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40981</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59230</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -15255,32 +15255,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -15290,32 +15290,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>49385</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37356</t>
+          <t>40367</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54012</t>
+          <t>59223</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -15325,32 +15325,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>52386</t>
+          <t>56909</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42832</t>
+          <t>47237</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61788</t>
+          <t>67647</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -15368,32 +15368,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39824</t>
+          <t>42004</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45790</t>
+          <t>48969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -15403,32 +15403,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>117869</t>
+          <t>127446</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108227</t>
+          <t>117105</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127233</t>
+          <t>137364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -15438,32 +15438,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>157693</t>
+          <t>169450</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145043</t>
+          <t>156558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168095</t>
+          <t>182892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -15481,7 +15481,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -15491,12 +15491,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -15516,32 +15516,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -15551,32 +15551,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>15176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -15594,32 +15594,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -15629,32 +15629,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36363</t>
+          <t>39630</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29274</t>
+          <t>32136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44791</t>
+          <t>49259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -15664,32 +15664,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>51336</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38178</t>
+          <t>41884</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>62873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -15707,32 +15707,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24190</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -15742,32 +15742,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55919</t>
+          <t>60196</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47637</t>
+          <t>51495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64939</t>
+          <t>70699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -15777,32 +15777,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73738</t>
+          <t>79194</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62777</t>
+          <t>68307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84437</t>
+          <t>91040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>342</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -15830,12 +15830,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>688</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -16081,32 +16081,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16116,22 +16116,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -16163,32 +16163,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16198,32 +16198,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16233,32 +16233,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -16276,32 +16276,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13976</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -16311,32 +16311,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16346,32 +16346,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -16389,32 +16389,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -16424,32 +16424,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -16459,32 +16459,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -16502,32 +16502,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -16537,32 +16537,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -16572,32 +16572,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>31397</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23393</t>
+          <t>25035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35502</t>
+          <t>38325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,0%</t>
         </is>
       </c>
     </row>
@@ -16615,32 +16615,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -16650,7 +16650,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>562</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -16660,12 +16660,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -16685,32 +16685,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -16728,32 +16728,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -16763,32 +16763,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -16798,32 +16798,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -16841,32 +16841,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -16876,32 +16876,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16507</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -16911,32 +16911,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>690</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -16964,12 +16964,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -16999,12 +16999,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -17024,32 +17024,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>465</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>648</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -17190,12 +17190,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>433</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -17225,12 +17225,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -17260,12 +17260,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -17307,12 +17307,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -17332,32 +17332,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -17367,32 +17367,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -17410,32 +17410,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -17455,12 +17455,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17480,32 +17480,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>925</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -17533,12 +17533,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -17558,32 +17558,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -17593,32 +17593,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>858</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -17636,32 +17636,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -17671,32 +17671,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2436</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -17706,32 +17706,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>925</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -17759,12 +17759,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -17784,7 +17784,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>645</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -17794,12 +17794,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -17809,7 +17809,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -17829,12 +17829,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -17862,7 +17862,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -17872,12 +17872,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>890</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -17907,12 +17907,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -17932,32 +17932,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -18010,7 +18010,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -18020,12 +18020,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18045,7 +18045,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -18055,12 +18055,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -18431,32 +18431,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -18466,32 +18466,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -18501,17 +18501,17 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>13228</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>25730</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -18521,12 +18521,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -18544,32 +18544,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>39156</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>29228</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>43956</t>
+          <t>47317</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -18579,32 +18579,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>36915</t>
+          <t>41340</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>46268</t>
+          <t>51163</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -18614,32 +18614,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>73058</t>
+          <t>80496</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>68689</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>84692</t>
+          <t>92688</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -18657,32 +18657,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -18692,32 +18692,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>58690</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>45448</t>
+          <t>48655</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>63414</t>
+          <t>69294</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -18727,32 +18727,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>66911</t>
+          <t>72950</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>56351</t>
+          <t>61681</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>77628</t>
+          <t>84690</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -18770,32 +18770,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>51153</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>43476</t>
+          <t>45578</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>59017</t>
+          <t>62386</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -18805,32 +18805,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>139491</t>
+          <t>151307</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>127485</t>
+          <t>138967</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>150062</t>
+          <t>162859</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -18840,32 +18840,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>190644</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>176554</t>
+          <t>190634</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>203581</t>
+          <t>219723</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -18883,32 +18883,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8626</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -18918,32 +18918,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -18953,32 +18953,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -18996,32 +18996,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>22237</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -19031,32 +19031,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>45158</t>
+          <t>49214</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>53818</t>
+          <t>59342</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19066,32 +19066,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>60357</t>
+          <t>65309</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>51759</t>
+          <t>55257</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>70742</t>
+          <t>77801</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -19109,32 +19109,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19144,32 +19144,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>68974</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>58929</t>
+          <t>65561</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>79200</t>
+          <t>86489</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19179,32 +19179,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>98775</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>80059</t>
+          <t>85785</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>103923</t>
+          <t>111380</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -19247,7 +19247,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19257,22 +19257,22 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>460</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19292,32 +19292,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -19448,7 +19448,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -19483,32 +19483,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -19518,17 +19518,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -19538,12 +19538,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
